--- a/orcamento/valores_exames_samvida.xlsx
+++ b/orcamento/valores_exames_samvida.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
   <si>
     <t>Local</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>ELETROCARDIOGRAMA</t>
+  </si>
+  <si>
+    <t>ELETRONEUROMIOGRAFIA</t>
   </si>
   <si>
     <t xml:space="preserve">ENDOSCOPIA DIGESTIVA ALTA</t>
@@ -2740,7 +2743,7 @@
         <v>54</v>
       </c>
       <c r="C52" s="7">
-        <v>410</v>
+        <v>530</v>
       </c>
     </row>
     <row r="53" ht="14.25">
@@ -2751,7 +2754,7 @@
         <v>55</v>
       </c>
       <c r="C53" s="7">
-        <v>106</v>
+        <v>410</v>
       </c>
     </row>
     <row r="54" ht="14.25">
@@ -2762,7 +2765,7 @@
         <v>56</v>
       </c>
       <c r="C54" s="7">
-        <v>156</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -2773,7 +2776,7 @@
         <v>57</v>
       </c>
       <c r="C55" s="7">
-        <v>106</v>
+        <v>156</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -2795,7 +2798,7 @@
         <v>59</v>
       </c>
       <c r="C57" s="7">
-        <v>156</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58" ht="14.25">
@@ -2806,7 +2809,7 @@
         <v>60</v>
       </c>
       <c r="C58" s="7">
-        <v>16</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" ht="14.25">
@@ -2817,7 +2820,7 @@
         <v>61</v>
       </c>
       <c r="C59" s="7">
-        <v>556</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" ht="14.25">
@@ -2828,7 +2831,7 @@
         <v>62</v>
       </c>
       <c r="C60" s="7">
-        <v>506</v>
+        <v>556</v>
       </c>
     </row>
     <row r="61" ht="14.25">
@@ -2839,7 +2842,7 @@
         <v>63</v>
       </c>
       <c r="C61" s="7">
-        <v>656</v>
+        <v>506</v>
       </c>
     </row>
     <row r="62" ht="14.25">
@@ -2850,7 +2853,7 @@
         <v>64</v>
       </c>
       <c r="C62" s="7">
-        <v>906</v>
+        <v>656</v>
       </c>
     </row>
     <row r="63" ht="14.25">
@@ -2861,7 +2864,7 @@
         <v>65</v>
       </c>
       <c r="C63" s="7">
-        <v>1006</v>
+        <v>906</v>
       </c>
     </row>
     <row r="64" ht="14.25">
@@ -2872,7 +2875,7 @@
         <v>66</v>
       </c>
       <c r="C64" s="7">
-        <v>466</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="65" ht="14.25">
@@ -2883,7 +2886,7 @@
         <v>67</v>
       </c>
       <c r="C65" s="7">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="66" ht="14.25">
@@ -2894,7 +2897,7 @@
         <v>68</v>
       </c>
       <c r="C66" s="7">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="67" ht="14.25">
@@ -2905,7 +2908,7 @@
         <v>69</v>
       </c>
       <c r="C67" s="7">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="68" ht="14.25">
@@ -2916,7 +2919,7 @@
         <v>70</v>
       </c>
       <c r="C68" s="7">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="69" ht="14.25">
@@ -2938,7 +2941,7 @@
         <v>72</v>
       </c>
       <c r="C70" s="7">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="71" ht="14.25">
@@ -2971,7 +2974,7 @@
         <v>75</v>
       </c>
       <c r="C73" s="7">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="74" ht="14.25">
@@ -2993,7 +2996,7 @@
         <v>77</v>
       </c>
       <c r="C75" s="7">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="76" ht="14.25">
@@ -3004,7 +3007,7 @@
         <v>78</v>
       </c>
       <c r="C76" s="7">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="77" ht="14.25">
@@ -3033,11 +3036,11 @@
       <c r="A79" t="s">
         <v>3</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C79" s="9">
-        <v>611</v>
+      <c r="C79" s="7">
+        <v>466</v>
       </c>
     </row>
     <row r="80" ht="14.25">
@@ -3048,7 +3051,7 @@
         <v>82</v>
       </c>
       <c r="C80" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="81" ht="14.25">
@@ -3059,7 +3062,7 @@
         <v>83</v>
       </c>
       <c r="C81" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="82" ht="14.25">
@@ -3070,7 +3073,7 @@
         <v>84</v>
       </c>
       <c r="C82" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="83" ht="14.25">
@@ -3081,7 +3084,7 @@
         <v>85</v>
       </c>
       <c r="C83" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="84" ht="14.25">
@@ -3092,7 +3095,7 @@
         <v>86</v>
       </c>
       <c r="C84" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="85" ht="14.25">
@@ -3114,7 +3117,7 @@
         <v>88</v>
       </c>
       <c r="C86" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="87" ht="14.25">
@@ -3136,7 +3139,7 @@
         <v>90</v>
       </c>
       <c r="C88" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="89" ht="14.25">
@@ -3147,7 +3150,7 @@
         <v>91</v>
       </c>
       <c r="C89" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="90" ht="14.25">
@@ -3158,7 +3161,7 @@
         <v>92</v>
       </c>
       <c r="C90" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="91" ht="14.25">
@@ -3169,7 +3172,7 @@
         <v>93</v>
       </c>
       <c r="C91" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="92" ht="14.25">
@@ -3180,7 +3183,7 @@
         <v>94</v>
       </c>
       <c r="C92" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="93" ht="14.25">
@@ -3191,7 +3194,7 @@
         <v>95</v>
       </c>
       <c r="C93" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="94" ht="14.25">
@@ -3202,7 +3205,7 @@
         <v>96</v>
       </c>
       <c r="C94" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="95" ht="14.25">
@@ -3224,7 +3227,7 @@
         <v>98</v>
       </c>
       <c r="C96" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="97" ht="14.25">
@@ -3235,7 +3238,7 @@
         <v>99</v>
       </c>
       <c r="C97" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="98" ht="14.25">
@@ -3246,7 +3249,7 @@
         <v>100</v>
       </c>
       <c r="C98" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="99" ht="14.25">
@@ -3257,7 +3260,7 @@
         <v>101</v>
       </c>
       <c r="C99" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="100" ht="14.25">
@@ -3268,7 +3271,7 @@
         <v>102</v>
       </c>
       <c r="C100" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="101" ht="14.25">
@@ -3279,7 +3282,7 @@
         <v>103</v>
       </c>
       <c r="C101" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="102" ht="14.25">
@@ -3290,7 +3293,7 @@
         <v>104</v>
       </c>
       <c r="C102" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="103" ht="14.25">
@@ -3301,7 +3304,7 @@
         <v>105</v>
       </c>
       <c r="C103" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="104" ht="14.25">
@@ -3312,7 +3315,7 @@
         <v>106</v>
       </c>
       <c r="C104" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="105" ht="14.25">
@@ -3323,7 +3326,7 @@
         <v>107</v>
       </c>
       <c r="C105" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="106" ht="14.25">
@@ -3334,7 +3337,7 @@
         <v>108</v>
       </c>
       <c r="C106" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="107" ht="14.25">
@@ -3345,7 +3348,7 @@
         <v>109</v>
       </c>
       <c r="C107" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="108" ht="14.25">
@@ -3356,7 +3359,7 @@
         <v>110</v>
       </c>
       <c r="C108" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="109" ht="14.25">
@@ -3367,7 +3370,7 @@
         <v>111</v>
       </c>
       <c r="C109" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="110" ht="14.25">
@@ -3378,7 +3381,7 @@
         <v>112</v>
       </c>
       <c r="C110" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="111" ht="14.25">
@@ -3389,7 +3392,7 @@
         <v>113</v>
       </c>
       <c r="C111" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="112" ht="14.25">
@@ -3400,7 +3403,7 @@
         <v>114</v>
       </c>
       <c r="C112" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="113" ht="14.25">
@@ -3411,7 +3414,7 @@
         <v>115</v>
       </c>
       <c r="C113" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="114" ht="14.25">
@@ -3422,7 +3425,7 @@
         <v>116</v>
       </c>
       <c r="C114" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="115" ht="14.25">
@@ -3433,7 +3436,7 @@
         <v>117</v>
       </c>
       <c r="C115" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="116" ht="14.25">
@@ -3444,7 +3447,7 @@
         <v>118</v>
       </c>
       <c r="C116" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="117" ht="14.25">
@@ -3455,7 +3458,7 @@
         <v>119</v>
       </c>
       <c r="C117" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="118" ht="14.25">
@@ -3466,7 +3469,7 @@
         <v>120</v>
       </c>
       <c r="C118" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="119" ht="14.25">
@@ -3477,7 +3480,7 @@
         <v>121</v>
       </c>
       <c r="C119" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="120" ht="14.25">
@@ -3532,7 +3535,7 @@
         <v>126</v>
       </c>
       <c r="C124" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="125" ht="14.25">
@@ -3543,7 +3546,7 @@
         <v>127</v>
       </c>
       <c r="C125" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="126" ht="14.25">
@@ -3554,7 +3557,7 @@
         <v>128</v>
       </c>
       <c r="C126" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="127" ht="14.25">
@@ -3565,7 +3568,7 @@
         <v>129</v>
       </c>
       <c r="C127" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="128" ht="14.25">
@@ -3576,7 +3579,7 @@
         <v>130</v>
       </c>
       <c r="C128" s="9">
-        <v>486</v>
+        <v>466</v>
       </c>
     </row>
     <row r="129" ht="14.25">
@@ -3587,7 +3590,7 @@
         <v>131</v>
       </c>
       <c r="C129" s="9">
-        <v>611</v>
+        <v>486</v>
       </c>
     </row>
     <row r="130" ht="14.25">
@@ -3598,7 +3601,7 @@
         <v>132</v>
       </c>
       <c r="C130" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="131" ht="14.25">
@@ -3609,7 +3612,7 @@
         <v>133</v>
       </c>
       <c r="C131" s="9">
-        <v>486</v>
+        <v>466</v>
       </c>
     </row>
     <row r="132" ht="14.25">
@@ -3620,7 +3623,7 @@
         <v>134</v>
       </c>
       <c r="C132" s="9">
-        <v>611</v>
+        <v>486</v>
       </c>
     </row>
     <row r="133" ht="14.25">
@@ -3631,7 +3634,7 @@
         <v>135</v>
       </c>
       <c r="C133" s="9">
-        <v>866</v>
+        <v>611</v>
       </c>
     </row>
     <row r="134" ht="14.25">
@@ -3653,7 +3656,7 @@
         <v>137</v>
       </c>
       <c r="C135" s="9">
-        <v>466</v>
+        <v>866</v>
       </c>
     </row>
     <row r="136" ht="14.25">
@@ -3664,7 +3667,7 @@
         <v>138</v>
       </c>
       <c r="C136" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="137" ht="14.25">
@@ -3675,7 +3678,7 @@
         <v>139</v>
       </c>
       <c r="C137" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="138" ht="14.25">
@@ -3686,7 +3689,7 @@
         <v>140</v>
       </c>
       <c r="C138" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="139" ht="14.25">
@@ -3697,7 +3700,7 @@
         <v>141</v>
       </c>
       <c r="C139" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="140" ht="14.25">
@@ -3708,7 +3711,7 @@
         <v>142</v>
       </c>
       <c r="C140" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="141" ht="14.25">
@@ -3719,7 +3722,7 @@
         <v>143</v>
       </c>
       <c r="C141" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="142" ht="14.25">
@@ -3741,7 +3744,7 @@
         <v>145</v>
       </c>
       <c r="C143" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="144" ht="14.25">
@@ -3752,7 +3755,7 @@
         <v>146</v>
       </c>
       <c r="C144" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="145" ht="14.25">
@@ -3763,7 +3766,7 @@
         <v>147</v>
       </c>
       <c r="C145" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="146" ht="14.25">
@@ -3774,7 +3777,7 @@
         <v>148</v>
       </c>
       <c r="C146" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="147" ht="14.25">
@@ -3785,7 +3788,7 @@
         <v>149</v>
       </c>
       <c r="C147" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="148" ht="14.25">
@@ -3796,7 +3799,7 @@
         <v>150</v>
       </c>
       <c r="C148" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="149" ht="14.25">
@@ -3807,7 +3810,7 @@
         <v>151</v>
       </c>
       <c r="C149" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="150" ht="14.25">
@@ -3818,7 +3821,7 @@
         <v>152</v>
       </c>
       <c r="C150" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="151" ht="14.25">
@@ -3829,7 +3832,7 @@
         <v>153</v>
       </c>
       <c r="C151" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="152" ht="14.25">
@@ -3840,7 +3843,7 @@
         <v>154</v>
       </c>
       <c r="C152" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="153" ht="14.25">
@@ -3851,7 +3854,7 @@
         <v>155</v>
       </c>
       <c r="C153" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="154" ht="14.25">
@@ -3862,7 +3865,7 @@
         <v>156</v>
       </c>
       <c r="C154" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="155" ht="14.25">
@@ -3873,7 +3876,7 @@
         <v>157</v>
       </c>
       <c r="C155" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="156" ht="14.25">
@@ -3884,7 +3887,7 @@
         <v>158</v>
       </c>
       <c r="C156" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="157" ht="14.25">
@@ -3895,7 +3898,7 @@
         <v>159</v>
       </c>
       <c r="C157" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="158" ht="14.25">
@@ -3906,7 +3909,7 @@
         <v>160</v>
       </c>
       <c r="C158" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="159" ht="14.25">
@@ -3917,7 +3920,7 @@
         <v>161</v>
       </c>
       <c r="C159" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="160" ht="14.25">
@@ -3928,7 +3931,7 @@
         <v>162</v>
       </c>
       <c r="C160" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="161" ht="14.25">
@@ -3939,7 +3942,7 @@
         <v>163</v>
       </c>
       <c r="C161" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="162" ht="14.25">
@@ -3950,7 +3953,7 @@
         <v>164</v>
       </c>
       <c r="C162" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="163" ht="14.25">
@@ -3961,7 +3964,7 @@
         <v>165</v>
       </c>
       <c r="C163" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="164" ht="14.25">
@@ -3972,7 +3975,7 @@
         <v>166</v>
       </c>
       <c r="C164" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="165" ht="14.25">
@@ -3983,7 +3986,7 @@
         <v>167</v>
       </c>
       <c r="C165" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="166" ht="14.25">
@@ -3994,7 +3997,7 @@
         <v>168</v>
       </c>
       <c r="C166" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="167" ht="14.25">
@@ -4016,7 +4019,7 @@
         <v>170</v>
       </c>
       <c r="C168" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="169" ht="14.25">
@@ -4038,7 +4041,7 @@
         <v>172</v>
       </c>
       <c r="C170" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="171" ht="14.25">
@@ -4049,7 +4052,7 @@
         <v>173</v>
       </c>
       <c r="C171" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="172" ht="14.25">
@@ -4060,7 +4063,7 @@
         <v>174</v>
       </c>
       <c r="C172" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="173" ht="14.25">
@@ -4071,7 +4074,7 @@
         <v>175</v>
       </c>
       <c r="C173" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="174" ht="14.25">
@@ -4082,7 +4085,7 @@
         <v>176</v>
       </c>
       <c r="C174" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="175" ht="14.25">
@@ -4093,7 +4096,7 @@
         <v>177</v>
       </c>
       <c r="C175" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="176" ht="14.25">
@@ -4104,7 +4107,7 @@
         <v>178</v>
       </c>
       <c r="C176" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="177" ht="14.25">
@@ -4115,7 +4118,7 @@
         <v>179</v>
       </c>
       <c r="C177" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="178" ht="14.25">
@@ -4148,7 +4151,7 @@
         <v>182</v>
       </c>
       <c r="C180" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="181" ht="14.25">
@@ -4181,7 +4184,7 @@
         <v>185</v>
       </c>
       <c r="C183" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="184" ht="14.25">
@@ -4192,7 +4195,7 @@
         <v>186</v>
       </c>
       <c r="C184" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="185" ht="14.25">
@@ -4203,7 +4206,7 @@
         <v>187</v>
       </c>
       <c r="C185" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="186" ht="14.25">
@@ -4214,7 +4217,7 @@
         <v>188</v>
       </c>
       <c r="C186" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="187" ht="14.25">
@@ -4225,7 +4228,7 @@
         <v>189</v>
       </c>
       <c r="C187" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="188" ht="14.25">
@@ -4236,7 +4239,7 @@
         <v>190</v>
       </c>
       <c r="C188" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="189" ht="14.25">
@@ -4247,7 +4250,7 @@
         <v>191</v>
       </c>
       <c r="C189" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="190" ht="14.25">
@@ -4258,7 +4261,7 @@
         <v>192</v>
       </c>
       <c r="C190" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="191" ht="14.25">
@@ -4269,7 +4272,7 @@
         <v>193</v>
       </c>
       <c r="C191" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="192" ht="14.25">
@@ -4280,7 +4283,7 @@
         <v>194</v>
       </c>
       <c r="C192" s="9">
-        <v>506</v>
+        <v>611</v>
       </c>
     </row>
     <row r="193" ht="14.25">
@@ -4291,7 +4294,7 @@
         <v>195</v>
       </c>
       <c r="C193" s="9">
-        <v>611</v>
+        <v>506</v>
       </c>
     </row>
     <row r="194" ht="14.25">
@@ -4302,7 +4305,7 @@
         <v>196</v>
       </c>
       <c r="C194" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="195" ht="14.25">
@@ -4313,7 +4316,7 @@
         <v>197</v>
       </c>
       <c r="C195" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" ht="14.25">
@@ -4324,7 +4327,7 @@
         <v>198</v>
       </c>
       <c r="C196" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="197" ht="14.25">
@@ -4335,7 +4338,7 @@
         <v>199</v>
       </c>
       <c r="C197" s="9">
-        <v>611</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" ht="14.25">
@@ -4346,7 +4349,7 @@
         <v>200</v>
       </c>
       <c r="C198" s="9">
-        <v>466</v>
+        <v>611</v>
       </c>
     </row>
     <row r="199" ht="14.25">
@@ -4357,7 +4360,7 @@
         <v>201</v>
       </c>
       <c r="C199" s="9">
-        <v>56</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" ht="14.25">
@@ -4731,7 +4734,7 @@
         <v>235</v>
       </c>
       <c r="C233" s="9">
-        <v>156</v>
+        <v>56</v>
       </c>
     </row>
     <row r="234" ht="14.25">
@@ -4742,7 +4745,7 @@
         <v>236</v>
       </c>
       <c r="C234" s="9">
-        <v>56</v>
+        <v>156</v>
       </c>
     </row>
     <row r="235" ht="14.25">
@@ -4852,7 +4855,7 @@
         <v>246</v>
       </c>
       <c r="C244" s="9">
-        <v>126</v>
+        <v>56</v>
       </c>
     </row>
     <row r="245" ht="14.25">
@@ -4863,7 +4866,7 @@
         <v>247</v>
       </c>
       <c r="C245" s="9">
-        <v>156</v>
+        <v>126</v>
       </c>
     </row>
     <row r="246" ht="14.25">
@@ -4874,7 +4877,7 @@
         <v>248</v>
       </c>
       <c r="C246" s="9">
-        <v>56</v>
+        <v>156</v>
       </c>
     </row>
     <row r="247" ht="14.25">
@@ -4885,7 +4888,7 @@
         <v>249</v>
       </c>
       <c r="C247" s="9">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="248" ht="14.25">
@@ -4940,7 +4943,7 @@
         <v>254</v>
       </c>
       <c r="C252" s="9">
-        <v>56</v>
+        <v>21</v>
       </c>
     </row>
     <row r="253" ht="14.25">
@@ -5094,7 +5097,7 @@
         <v>268</v>
       </c>
       <c r="C266" s="9">
-        <v>156</v>
+        <v>56</v>
       </c>
     </row>
     <row r="267" ht="14.25">
@@ -5116,7 +5119,7 @@
         <v>270</v>
       </c>
       <c r="C268" s="9">
-        <v>56</v>
+        <v>156</v>
       </c>
     </row>
     <row r="269" ht="14.25">
@@ -5347,7 +5350,7 @@
         <v>291</v>
       </c>
       <c r="C289" s="9">
-        <v>406</v>
+        <v>56</v>
       </c>
     </row>
     <row r="290" ht="14.25">
@@ -5358,7 +5361,7 @@
         <v>292</v>
       </c>
       <c r="C290" s="9">
-        <v>476</v>
+        <v>406</v>
       </c>
     </row>
     <row r="291" ht="14.25">
@@ -5380,7 +5383,7 @@
         <v>294</v>
       </c>
       <c r="C292" s="9">
-        <v>556</v>
+        <v>476</v>
       </c>
     </row>
     <row r="293" ht="14.25">
@@ -5391,7 +5394,7 @@
         <v>295</v>
       </c>
       <c r="C293" s="9">
-        <v>271</v>
+        <v>556</v>
       </c>
     </row>
     <row r="294" ht="14.25">
@@ -5413,7 +5416,7 @@
         <v>297</v>
       </c>
       <c r="C295" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="296" ht="14.25">
@@ -5435,7 +5438,7 @@
         <v>299</v>
       </c>
       <c r="C297" s="9">
-        <v>476</v>
+        <v>356</v>
       </c>
     </row>
     <row r="298" ht="14.25">
@@ -5446,7 +5449,7 @@
         <v>300</v>
       </c>
       <c r="C298" s="9">
-        <v>271</v>
+        <v>476</v>
       </c>
     </row>
     <row r="299" ht="14.25">
@@ -5501,7 +5504,7 @@
         <v>305</v>
       </c>
       <c r="C303" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="304" ht="14.25">
@@ -5512,7 +5515,7 @@
         <v>306</v>
       </c>
       <c r="C304" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="305" ht="14.25">
@@ -5523,7 +5526,7 @@
         <v>307</v>
       </c>
       <c r="C305" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="306" ht="14.25">
@@ -5534,7 +5537,7 @@
         <v>308</v>
       </c>
       <c r="C306" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="307" ht="14.25">
@@ -5545,7 +5548,7 @@
         <v>309</v>
       </c>
       <c r="C307" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="308" ht="14.25">
@@ -5556,7 +5559,7 @@
         <v>310</v>
       </c>
       <c r="C308" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="309" ht="14.25">
@@ -5567,7 +5570,7 @@
         <v>311</v>
       </c>
       <c r="C309" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="310" ht="14.25">
@@ -5578,7 +5581,7 @@
         <v>312</v>
       </c>
       <c r="C310" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="311" ht="14.25">
@@ -5589,7 +5592,7 @@
         <v>313</v>
       </c>
       <c r="C311" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="312" ht="14.25">
@@ -5600,7 +5603,7 @@
         <v>314</v>
       </c>
       <c r="C312" s="9">
-        <v>46</v>
+        <v>356</v>
       </c>
     </row>
     <row r="313" ht="14.25">
@@ -5611,7 +5614,7 @@
         <v>315</v>
       </c>
       <c r="C313" s="9">
-        <v>271</v>
+        <v>46</v>
       </c>
     </row>
     <row r="314" ht="14.25">
@@ -5622,7 +5625,7 @@
         <v>316</v>
       </c>
       <c r="C314" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="315" ht="14.25">
@@ -5633,7 +5636,7 @@
         <v>317</v>
       </c>
       <c r="C315" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="316" ht="14.25">
@@ -5644,7 +5647,7 @@
         <v>318</v>
       </c>
       <c r="C316" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="317" ht="14.25">
@@ -5655,7 +5658,7 @@
         <v>319</v>
       </c>
       <c r="C317" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="318" ht="14.25">
@@ -5666,7 +5669,7 @@
         <v>320</v>
       </c>
       <c r="C318" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="319" ht="14.25">
@@ -5677,7 +5680,7 @@
         <v>321</v>
       </c>
       <c r="C319" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="320" ht="14.25">
@@ -5688,7 +5691,7 @@
         <v>322</v>
       </c>
       <c r="C320" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="321" ht="14.25">
@@ -5699,7 +5702,7 @@
         <v>323</v>
       </c>
       <c r="C321" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="322" ht="14.25">
@@ -5710,7 +5713,7 @@
         <v>324</v>
       </c>
       <c r="C322" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="323" ht="14.25">
@@ -5721,7 +5724,7 @@
         <v>325</v>
       </c>
       <c r="C323" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="324" ht="14.25">
@@ -5732,7 +5735,7 @@
         <v>326</v>
       </c>
       <c r="C324" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="325" ht="14.25">
@@ -5743,7 +5746,7 @@
         <v>327</v>
       </c>
       <c r="C325" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="326" ht="14.25">
@@ -5754,7 +5757,7 @@
         <v>328</v>
       </c>
       <c r="C326" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="327" ht="14.25">
@@ -5765,7 +5768,7 @@
         <v>329</v>
       </c>
       <c r="C327" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="328" ht="14.25">
@@ -5776,7 +5779,7 @@
         <v>330</v>
       </c>
       <c r="C328" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="329" ht="14.25">
@@ -5798,7 +5801,7 @@
         <v>332</v>
       </c>
       <c r="C330" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="331" ht="14.25">
@@ -5820,7 +5823,7 @@
         <v>334</v>
       </c>
       <c r="C332" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="333" ht="14.25">
@@ -5831,7 +5834,7 @@
         <v>335</v>
       </c>
       <c r="C333" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="334" ht="14.25">
@@ -5842,7 +5845,7 @@
         <v>336</v>
       </c>
       <c r="C334" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="335" ht="14.25">
@@ -5853,7 +5856,7 @@
         <v>337</v>
       </c>
       <c r="C335" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="336" ht="14.25">
@@ -5875,7 +5878,7 @@
         <v>339</v>
       </c>
       <c r="C337" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="338" ht="14.25">
@@ -5886,7 +5889,7 @@
         <v>340</v>
       </c>
       <c r="C338" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="339" ht="14.25">
@@ -5897,7 +5900,7 @@
         <v>341</v>
       </c>
       <c r="C339" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="340" ht="14.25">
@@ -5908,7 +5911,7 @@
         <v>342</v>
       </c>
       <c r="C340" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="341" ht="14.25">
@@ -5919,7 +5922,7 @@
         <v>343</v>
       </c>
       <c r="C341" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="342" ht="14.25">
@@ -5930,7 +5933,7 @@
         <v>344</v>
       </c>
       <c r="C342" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="343" ht="14.25">
@@ -5941,7 +5944,7 @@
         <v>345</v>
       </c>
       <c r="C343" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="344" ht="14.25">
@@ -5952,7 +5955,7 @@
         <v>346</v>
       </c>
       <c r="C344" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="345" ht="14.25">
@@ -5963,7 +5966,7 @@
         <v>347</v>
       </c>
       <c r="C345" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="346" ht="14.25">
@@ -5974,7 +5977,7 @@
         <v>348</v>
       </c>
       <c r="C346" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="347" ht="14.25">
@@ -5985,7 +5988,7 @@
         <v>349</v>
       </c>
       <c r="C347" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="348" ht="14.25">
@@ -5996,7 +5999,7 @@
         <v>350</v>
       </c>
       <c r="C348" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="349" ht="14.25">
@@ -6007,7 +6010,7 @@
         <v>351</v>
       </c>
       <c r="C349" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="350" ht="14.25">
@@ -6018,7 +6021,7 @@
         <v>352</v>
       </c>
       <c r="C350" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="351" ht="14.25">
@@ -6029,7 +6032,7 @@
         <v>353</v>
       </c>
       <c r="C351" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="352" ht="14.25">
@@ -6040,7 +6043,7 @@
         <v>354</v>
       </c>
       <c r="C352" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="353" ht="14.25">
@@ -6051,7 +6054,7 @@
         <v>355</v>
       </c>
       <c r="C353" s="9">
-        <v>456</v>
+        <v>271</v>
       </c>
     </row>
     <row r="354" ht="14.25">
@@ -6062,7 +6065,7 @@
         <v>356</v>
       </c>
       <c r="C354" s="9">
-        <v>271</v>
+        <v>456</v>
       </c>
     </row>
     <row r="355" ht="14.25">
@@ -6073,7 +6076,7 @@
         <v>357</v>
       </c>
       <c r="C355" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="356" ht="14.25">
@@ -6084,7 +6087,7 @@
         <v>358</v>
       </c>
       <c r="C356" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="357" ht="14.25">
@@ -6095,7 +6098,7 @@
         <v>359</v>
       </c>
       <c r="C357" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="358" ht="14.25">
@@ -6106,7 +6109,7 @@
         <v>360</v>
       </c>
       <c r="C358" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="359" ht="14.25">
@@ -6117,7 +6120,7 @@
         <v>361</v>
       </c>
       <c r="C359" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="360" ht="14.25">
@@ -6128,7 +6131,7 @@
         <v>362</v>
       </c>
       <c r="C360" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="361" ht="14.25">
@@ -6139,7 +6142,7 @@
         <v>363</v>
       </c>
       <c r="C361" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="362" ht="14.25">
@@ -6150,7 +6153,7 @@
         <v>364</v>
       </c>
       <c r="C362" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="363" ht="14.25">
@@ -6161,7 +6164,7 @@
         <v>365</v>
       </c>
       <c r="C363" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="364" ht="14.25">
@@ -6172,7 +6175,7 @@
         <v>366</v>
       </c>
       <c r="C364" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="365" ht="14.25">
@@ -6183,7 +6186,7 @@
         <v>367</v>
       </c>
       <c r="C365" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="366" ht="14.25">
@@ -6194,7 +6197,7 @@
         <v>368</v>
       </c>
       <c r="C366" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="367" ht="14.25">
@@ -6205,7 +6208,7 @@
         <v>369</v>
       </c>
       <c r="C367" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="368" ht="14.25">
@@ -6216,7 +6219,7 @@
         <v>370</v>
       </c>
       <c r="C368" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="369" ht="14.25">
@@ -6227,7 +6230,7 @@
         <v>371</v>
       </c>
       <c r="C369" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="370" ht="14.25">
@@ -6238,7 +6241,7 @@
         <v>372</v>
       </c>
       <c r="C370" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="371" ht="14.25">
@@ -6249,7 +6252,7 @@
         <v>373</v>
       </c>
       <c r="C371" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="372" ht="14.25">
@@ -6260,7 +6263,7 @@
         <v>374</v>
       </c>
       <c r="C372" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="373" ht="14.25">
@@ -6271,7 +6274,7 @@
         <v>375</v>
       </c>
       <c r="C373" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="374" ht="14.25">
@@ -6282,7 +6285,7 @@
         <v>376</v>
       </c>
       <c r="C374" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="375" ht="14.25">
@@ -6293,7 +6296,7 @@
         <v>377</v>
       </c>
       <c r="C375" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="376" ht="14.25">
@@ -6304,7 +6307,7 @@
         <v>378</v>
       </c>
       <c r="C376" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="377" ht="14.25">
@@ -6315,7 +6318,7 @@
         <v>379</v>
       </c>
       <c r="C377" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="378" ht="14.25">
@@ -6337,7 +6340,7 @@
         <v>381</v>
       </c>
       <c r="C379" s="9">
-        <v>456</v>
+        <v>356</v>
       </c>
     </row>
     <row r="380" ht="14.25">
@@ -6348,7 +6351,7 @@
         <v>382</v>
       </c>
       <c r="C380" s="9">
-        <v>271</v>
+        <v>456</v>
       </c>
     </row>
     <row r="381" ht="14.25">
@@ -6359,7 +6362,7 @@
         <v>383</v>
       </c>
       <c r="C381" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="382" ht="14.25">
@@ -6370,7 +6373,7 @@
         <v>384</v>
       </c>
       <c r="C382" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="383" ht="14.25">
@@ -6381,7 +6384,7 @@
         <v>385</v>
       </c>
       <c r="C383" s="9">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="384" ht="14.25">
@@ -6392,7 +6395,7 @@
         <v>386</v>
       </c>
       <c r="C384" s="9">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="385" ht="14.25">
@@ -6414,7 +6417,7 @@
         <v>388</v>
       </c>
       <c r="C386" s="9">
-        <v>186</v>
+        <v>271</v>
       </c>
     </row>
     <row r="387" ht="14.25">
@@ -6425,18 +6428,18 @@
         <v>389</v>
       </c>
       <c r="C387" s="9">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="388" ht="13.800000000000001">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="388" ht="14.25">
       <c r="A388" t="s">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="B388" s="8" t="s">
         <v>390</v>
       </c>
       <c r="C388" s="9">
-        <v>26</v>
+        <v>226</v>
       </c>
     </row>
     <row r="389" ht="13.800000000000001">
@@ -6447,7 +6450,7 @@
         <v>391</v>
       </c>
       <c r="C389" s="9">
-        <v>140</v>
+        <v>26</v>
       </c>
     </row>
     <row r="390" ht="13.800000000000001">
@@ -6458,7 +6461,7 @@
         <v>392</v>
       </c>
       <c r="C390" s="9">
-        <v>80</v>
+        <v>140</v>
       </c>
     </row>
     <row r="391" ht="13.800000000000001">
@@ -6469,7 +6472,7 @@
         <v>393</v>
       </c>
       <c r="C391" s="9">
-        <v>160</v>
+        <v>80</v>
       </c>
     </row>
     <row r="392" ht="13.800000000000001">
@@ -6480,7 +6483,7 @@
         <v>394</v>
       </c>
       <c r="C392" s="9">
-        <v>90</v>
+        <v>160</v>
       </c>
     </row>
     <row r="393" ht="13.800000000000001">
@@ -6491,7 +6494,7 @@
         <v>395</v>
       </c>
       <c r="C393" s="9">
-        <v>130</v>
+        <v>90</v>
       </c>
     </row>
     <row r="394" ht="13.800000000000001">
@@ -6502,7 +6505,7 @@
         <v>396</v>
       </c>
       <c r="C394" s="9">
-        <v>160</v>
+        <v>130</v>
       </c>
     </row>
     <row r="395" ht="13.800000000000001">
@@ -6513,7 +6516,7 @@
         <v>397</v>
       </c>
       <c r="C395" s="9">
-        <v>110</v>
+        <v>160</v>
       </c>
     </row>
     <row r="396" ht="13.800000000000001">
@@ -6524,7 +6527,7 @@
         <v>398</v>
       </c>
       <c r="C396" s="9">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="397" ht="13.800000000000001">
@@ -6535,7 +6538,7 @@
         <v>399</v>
       </c>
       <c r="C397" s="9">
-        <v>140</v>
+        <v>86</v>
       </c>
     </row>
     <row r="398" ht="13.800000000000001">
@@ -6546,7 +6549,7 @@
         <v>400</v>
       </c>
       <c r="C398" s="9">
-        <v>80</v>
+        <v>140</v>
       </c>
     </row>
     <row r="399" ht="13.800000000000001">
@@ -6557,7 +6560,7 @@
         <v>401</v>
       </c>
       <c r="C399" s="9">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="400" ht="13.800000000000001">
@@ -6568,7 +6571,7 @@
         <v>402</v>
       </c>
       <c r="C400" s="9">
-        <v>140</v>
+        <v>66</v>
       </c>
     </row>
     <row r="401" ht="13.800000000000001">
@@ -6579,7 +6582,7 @@
         <v>403</v>
       </c>
       <c r="C401" s="9">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="402" ht="13.800000000000001">
@@ -6590,7 +6593,7 @@
         <v>404</v>
       </c>
       <c r="C402" s="9">
-        <v>66</v>
+        <v>90</v>
       </c>
     </row>
     <row r="403" ht="13.800000000000001">
@@ -6601,7 +6604,7 @@
         <v>405</v>
       </c>
       <c r="C403" s="9">
-        <v>170</v>
+        <v>66</v>
       </c>
     </row>
     <row r="404" ht="13.800000000000001">
@@ -6612,7 +6615,7 @@
         <v>406</v>
       </c>
       <c r="C404" s="9">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="405" ht="13.800000000000001">
@@ -6623,7 +6626,7 @@
         <v>407</v>
       </c>
       <c r="C405" s="9">
-        <v>145</v>
+        <v>110</v>
       </c>
     </row>
     <row r="406" ht="13.800000000000001">
@@ -6634,7 +6637,7 @@
         <v>408</v>
       </c>
       <c r="C406" s="9">
-        <v>100</v>
+        <v>145</v>
       </c>
     </row>
     <row r="407" ht="13.800000000000001">
@@ -6645,7 +6648,7 @@
         <v>409</v>
       </c>
       <c r="C407" s="9">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="408" ht="13.800000000000001">
@@ -6677,8 +6680,8 @@
       <c r="B410" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="C410" s="2">
-        <v>140</v>
+      <c r="C410" s="9">
+        <v>66</v>
       </c>
     </row>
     <row r="411" ht="13.800000000000001">
@@ -6689,7 +6692,7 @@
         <v>413</v>
       </c>
       <c r="C411" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
     </row>
     <row r="412" ht="13.800000000000001">
@@ -6699,12 +6702,12 @@
       <c r="B412" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="C412" s="9">
-        <v>140</v>
+      <c r="C412" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="413" ht="13.800000000000001">
-      <c r="A413" s="10" t="s">
+      <c r="A413" t="s">
         <v>52</v>
       </c>
       <c r="B413" s="8" t="s">
@@ -6722,18 +6725,18 @@
         <v>416</v>
       </c>
       <c r="C414" s="9">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="415" ht="13.800000000000001">
-      <c r="A415" t="s">
+      <c r="A415" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B415" s="8" t="s">
         <v>417</v>
       </c>
       <c r="C415" s="9">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="416" ht="13.800000000000001">
@@ -6744,7 +6747,7 @@
         <v>418</v>
       </c>
       <c r="C416" s="9">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="417" ht="13.800000000000001">
@@ -6755,7 +6758,7 @@
         <v>419</v>
       </c>
       <c r="C417" s="9">
-        <v>140</v>
+        <v>66</v>
       </c>
     </row>
     <row r="418" ht="13.800000000000001">
@@ -6766,7 +6769,7 @@
         <v>420</v>
       </c>
       <c r="C418" s="9">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="419" ht="13.800000000000001">
@@ -6777,7 +6780,7 @@
         <v>421</v>
       </c>
       <c r="C419" s="9">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="420" ht="13.800000000000001">
@@ -6788,7 +6791,7 @@
         <v>422</v>
       </c>
       <c r="C420" s="9">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="421" ht="13.800000000000001">
@@ -6890,42 +6893,42 @@
         <v>90</v>
       </c>
     </row>
-    <row r="430" ht="14.25">
+    <row r="430" ht="13.800000000000001">
       <c r="A430" t="s">
+        <v>52</v>
+      </c>
+      <c r="B430" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="B430" s="1" t="s">
+      <c r="C430" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="431" ht="14.25">
+      <c r="A431" t="s">
         <v>433</v>
-      </c>
-      <c r="C430" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="431" ht="13.800000000000001">
-      <c r="A431" t="s">
-        <v>432</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>434</v>
       </c>
       <c r="C431" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="432" ht="13.800000000000001">
       <c r="A432" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>435</v>
       </c>
       <c r="C432" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
     </row>
     <row r="433" ht="13.800000000000001">
       <c r="A433" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>436</v>
@@ -6936,7 +6939,7 @@
     </row>
     <row r="434" ht="13.800000000000001">
       <c r="A434" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>437</v>
@@ -6947,29 +6950,29 @@
     </row>
     <row r="435" ht="13.800000000000001">
       <c r="A435" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>438</v>
       </c>
       <c r="C435" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
     </row>
     <row r="436" ht="13.800000000000001">
       <c r="A436" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>439</v>
       </c>
       <c r="C436" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
     </row>
     <row r="437" ht="13.800000000000001">
       <c r="A437" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>440</v>
@@ -6980,7 +6983,7 @@
     </row>
     <row r="438" ht="13.800000000000001">
       <c r="A438" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>441</v>
@@ -6991,7 +6994,7 @@
     </row>
     <row r="439" ht="13.800000000000001">
       <c r="A439" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>442</v>
@@ -7002,7 +7005,7 @@
     </row>
     <row r="440" ht="13.800000000000001">
       <c r="A440" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>443</v>
@@ -7013,7 +7016,7 @@
     </row>
     <row r="441" ht="13.800000000000001">
       <c r="A441" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>444</v>
@@ -7024,7 +7027,7 @@
     </row>
     <row r="442" ht="13.800000000000001">
       <c r="A442" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>445</v>
@@ -7035,7 +7038,7 @@
     </row>
     <row r="443" ht="13.800000000000001">
       <c r="A443" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>446</v>
@@ -7046,7 +7049,7 @@
     </row>
     <row r="444" ht="13.800000000000001">
       <c r="A444" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>447</v>
@@ -7057,7 +7060,7 @@
     </row>
     <row r="445" ht="13.800000000000001">
       <c r="A445" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>448</v>
@@ -7068,7 +7071,7 @@
     </row>
     <row r="446" ht="13.800000000000001">
       <c r="A446" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>449</v>
@@ -7079,7 +7082,7 @@
     </row>
     <row r="447" ht="13.800000000000001">
       <c r="A447" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>450</v>
@@ -7090,7 +7093,7 @@
     </row>
     <row r="448" ht="13.800000000000001">
       <c r="A448" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>451</v>
@@ -7101,7 +7104,7 @@
     </row>
     <row r="449" ht="13.800000000000001">
       <c r="A449" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>452</v>
@@ -7112,7 +7115,7 @@
     </row>
     <row r="450" ht="13.800000000000001">
       <c r="A450" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>453</v>
@@ -7123,7 +7126,7 @@
     </row>
     <row r="451" ht="13.800000000000001">
       <c r="A451" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>454</v>
@@ -7134,7 +7137,7 @@
     </row>
     <row r="452" ht="13.800000000000001">
       <c r="A452" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>455</v>
@@ -7145,7 +7148,7 @@
     </row>
     <row r="453" ht="13.800000000000001">
       <c r="A453" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>456</v>
@@ -7156,7 +7159,7 @@
     </row>
     <row r="454" ht="13.800000000000001">
       <c r="A454" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>457</v>
@@ -7167,7 +7170,7 @@
     </row>
     <row r="455" ht="13.800000000000001">
       <c r="A455" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>458</v>
@@ -7178,7 +7181,7 @@
     </row>
     <row r="456" ht="13.800000000000001">
       <c r="A456" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>459</v>
@@ -7189,7 +7192,7 @@
     </row>
     <row r="457" ht="13.800000000000001">
       <c r="A457" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>460</v>
@@ -7200,7 +7203,7 @@
     </row>
     <row r="458" ht="13.800000000000001">
       <c r="A458" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>461</v>
@@ -7211,7 +7214,7 @@
     </row>
     <row r="459" ht="13.800000000000001">
       <c r="A459" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>462</v>
@@ -7222,7 +7225,7 @@
     </row>
     <row r="460" ht="13.800000000000001">
       <c r="A460" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>463</v>
@@ -7233,7 +7236,7 @@
     </row>
     <row r="461" ht="13.800000000000001">
       <c r="A461" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>464</v>
@@ -7244,7 +7247,7 @@
     </row>
     <row r="462" ht="13.800000000000001">
       <c r="A462" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>465</v>
@@ -7255,7 +7258,7 @@
     </row>
     <row r="463" ht="13.800000000000001">
       <c r="A463" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>466</v>
@@ -7266,7 +7269,7 @@
     </row>
     <row r="464" ht="13.800000000000001">
       <c r="A464" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>467</v>
@@ -7277,29 +7280,29 @@
     </row>
     <row r="465" ht="13.800000000000001">
       <c r="A465" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>468</v>
       </c>
       <c r="C465" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
     </row>
     <row r="466" ht="13.800000000000001">
       <c r="A466" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>469</v>
       </c>
       <c r="C466" s="2">
-        <v>80</v>
+        <v>140</v>
       </c>
     </row>
     <row r="467" ht="13.800000000000001">
       <c r="A467" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>470</v>
@@ -7310,7 +7313,7 @@
     </row>
     <row r="468" ht="13.800000000000001">
       <c r="A468" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>471</v>
@@ -7321,7 +7324,7 @@
     </row>
     <row r="469" ht="13.800000000000001">
       <c r="A469" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>472</v>
@@ -7332,7 +7335,7 @@
     </row>
     <row r="470" ht="13.800000000000001">
       <c r="A470" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>473</v>
@@ -7343,7 +7346,7 @@
     </row>
     <row r="471" ht="13.800000000000001">
       <c r="A471" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B471" s="1" t="s">
         <v>474</v>
@@ -7354,51 +7357,51 @@
     </row>
     <row r="472" ht="13.800000000000001">
       <c r="A472" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>475</v>
       </c>
       <c r="C472" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="473" ht="13.800000000000001">
       <c r="A473" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>476</v>
       </c>
       <c r="C473" s="2">
-        <v>160</v>
+        <v>100</v>
       </c>
     </row>
     <row r="474" ht="13.800000000000001">
       <c r="A474" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>477</v>
       </c>
       <c r="C474" s="2">
-        <v>100</v>
+        <v>160</v>
       </c>
     </row>
     <row r="475" ht="13.800000000000001">
       <c r="A475" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>478</v>
       </c>
       <c r="C475" s="2">
-        <v>160</v>
+        <v>100</v>
       </c>
     </row>
     <row r="476" ht="13.800000000000001">
       <c r="A476" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>479</v>
@@ -7409,29 +7412,29 @@
     </row>
     <row r="477" ht="13.800000000000001">
       <c r="A477" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>480</v>
       </c>
       <c r="C477" s="2">
-        <v>100</v>
+        <v>160</v>
       </c>
     </row>
     <row r="478" ht="13.800000000000001">
       <c r="A478" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>481</v>
       </c>
       <c r="C478" s="2">
-        <v>210</v>
+        <v>100</v>
       </c>
     </row>
     <row r="479" ht="13.800000000000001">
       <c r="A479" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>482</v>
@@ -7442,29 +7445,29 @@
     </row>
     <row r="480" ht="13.800000000000001">
       <c r="A480" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>483</v>
       </c>
       <c r="C480" s="2">
-        <v>310</v>
+        <v>210</v>
       </c>
     </row>
     <row r="481" ht="13.800000000000001">
       <c r="A481" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B481" s="1" t="s">
         <v>484</v>
       </c>
       <c r="C481" s="2">
-        <v>90</v>
+        <v>310</v>
       </c>
     </row>
     <row r="482" ht="13.800000000000001">
       <c r="A482" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>485</v>
@@ -7475,13 +7478,13 @@
     </row>
     <row r="483" ht="13.800000000000001">
       <c r="A483" t="s">
-        <v>52</v>
+        <v>433</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>486</v>
       </c>
       <c r="C483" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="484" ht="13.800000000000001">
@@ -7492,10 +7495,10 @@
         <v>487</v>
       </c>
       <c r="C484" s="2">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="485" ht="14.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="485" ht="13.800000000000001">
       <c r="A485" t="s">
         <v>52</v>
       </c>
@@ -7503,7 +7506,7 @@
         <v>488</v>
       </c>
       <c r="C485" s="2">
-        <v>210</v>
+        <v>160</v>
       </c>
     </row>
     <row r="486" ht="14.25">
@@ -7514,10 +7517,10 @@
         <v>489</v>
       </c>
       <c r="C486" s="2">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="487" ht="13.800000000000001">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="487" ht="14.25">
       <c r="A487" t="s">
         <v>52</v>
       </c>
@@ -7525,7 +7528,7 @@
         <v>490</v>
       </c>
       <c r="C487" s="2">
-        <v>140</v>
+        <v>430</v>
       </c>
     </row>
     <row r="488" ht="13.800000000000001">
@@ -7536,14 +7539,24 @@
         <v>491</v>
       </c>
       <c r="C488" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="489" ht="13.800000000000001">
+      <c r="A489" t="s">
+        <v>52</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C489" s="2">
         <v>185</v>
       </c>
     </row>
-    <row r="1048271" ht="12.800000000000001"/>
     <row r="1048272" ht="12.800000000000001"/>
     <row r="1048273" ht="12.800000000000001"/>
     <row r="1048274" ht="12.800000000000001"/>
-    <row r="1048572" ht="12.800000000000001"/>
+    <row r="1048275" ht="12.800000000000001"/>
     <row r="1048573" ht="12.800000000000001"/>
     <row r="1048574" ht="12.800000000000001"/>
     <row r="1048575" ht="12.800000000000001"/>
